--- a/Data/UX_Headset_Competitive_Analysis.xlsx
+++ b/Data/UX_Headset_Competitive_Analysis.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chelseamyers/Library/CloudStorage/Dropbox/Mac (2)/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fullsailedu-my.sharepoint.com/personal/chelseam_fullsail_com/Documents/Desktop/UX Research Analytics/User_Experience_Research_Analytics/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{553E6E7D-AA60-9742-87FB-3EBA5474C3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{553E6E7D-AA60-9742-87FB-3EBA5474C3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D66A64A-3497-41D1-BE70-8B86AE6F0E69}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="25280" windowHeight="14940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Headset Brands" sheetId="1" r:id="rId1"/>
+    <sheet name="Grip Comparison" sheetId="2" r:id="rId2"/>
+    <sheet name="Comfort Head Strap Comparison" sheetId="3" r:id="rId3"/>
+    <sheet name="VR Experience and Intent to Buy" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="22">
   <si>
     <t>UserID</t>
   </si>
@@ -43,9 +46,6 @@
     <t>ImmersionLevel</t>
   </si>
   <si>
-    <t>UserComment</t>
-  </si>
-  <si>
     <t>Male</t>
   </si>
   <si>
@@ -64,148 +64,31 @@
     <t>NeuroVisor</t>
   </si>
   <si>
-    <t>Decent experience, nothing extraordinary.</t>
+    <t>Grip A (s)</t>
   </si>
   <si>
-    <t>Felt like I was flying!</t>
+    <t>Grip B (s)</t>
   </si>
   <si>
-    <t>Average performance overall.</t>
+    <t>Subject</t>
   </si>
   <si>
-    <t>Stable, but not exciting.</t>
+    <t>Nausea_With_Comfort_Strap</t>
   </si>
   <si>
-    <t>Not very engaging, but comfortable.</t>
+    <t>Nausea_Without_Comfort_Strap</t>
   </si>
   <si>
-    <t>Mildly engaging but forgettable.</t>
+    <t>Previous VR Experience</t>
   </si>
   <si>
-    <t>Totally amazing and smooth!</t>
+    <t>No</t>
   </si>
   <si>
-    <t>Comfortable but not remarkable.</t>
+    <t>Yes</t>
   </si>
   <si>
-    <t>Simple setup.</t>
-  </si>
-  <si>
-    <t>Comfortable and immersive.</t>
-  </si>
-  <si>
-    <t>A basic session with room for improvement.</t>
-  </si>
-  <si>
-    <t>Felt kind of basic.</t>
-  </si>
-  <si>
-    <t>Incredibly immersive, felt truly present.</t>
-  </si>
-  <si>
-    <t>Boring and a bit queasy.</t>
-  </si>
-  <si>
-    <t>Lost track of reality, loved it.</t>
-  </si>
-  <si>
-    <t>Just an OK experience.</t>
-  </si>
-  <si>
-    <t>Functional but lacking wow factor.</t>
-  </si>
-  <si>
-    <t>Immersion was top-notch.</t>
-  </si>
-  <si>
-    <t>Mind-blowing visuals!</t>
-  </si>
-  <si>
-    <t>Solid but unexceptional.</t>
-  </si>
-  <si>
-    <t>Didn't blow me away, but good enough.</t>
-  </si>
-  <si>
-    <t>Felt like stepping into another world.</t>
-  </si>
-  <si>
-    <t>Started feeling queasy after a few minutes.</t>
-  </si>
-  <si>
-    <t>The depth of immersion was breathtaking.</t>
-  </si>
-  <si>
-    <t>Experienced significant nausea throughout.</t>
-  </si>
-  <si>
-    <t>Could barely stand the motion, felt sick.</t>
-  </si>
-  <si>
-    <t>Visited the virtual world but battled dizziness.</t>
-  </si>
-  <si>
-    <t>Totally absorbed in the environment.</t>
-  </si>
-  <si>
-    <t>Nausea struck hard during the experience.</t>
-  </si>
-  <si>
-    <t>Engrossing experience, highly immersive.</t>
-  </si>
-  <si>
-    <t>Unimpressed.</t>
-  </si>
-  <si>
-    <t>Wouldn't buy it.</t>
-  </si>
-  <si>
-    <t>Kind of cool.</t>
-  </si>
-  <si>
-    <t>Wouldn't be worth the money.</t>
-  </si>
-  <si>
-    <t>Just meh.</t>
-  </si>
-  <si>
-    <t>Really cool but I felt like I was going to barf.</t>
-  </si>
-  <si>
-    <t>So so so cool.</t>
-  </si>
-  <si>
-    <t>Really awesome.  Felt a little off but not too bad.</t>
-  </si>
-  <si>
-    <t>I loved it!  10/10!</t>
-  </si>
-  <si>
-    <t>Felt just like I was there but it did giv eme a bit of a headache.</t>
-  </si>
-  <si>
-    <t>I really liked it but I don't know if I could have used it much longer.</t>
-  </si>
-  <si>
-    <t>Boring.</t>
-  </si>
-  <si>
-    <t>Nothing special.</t>
-  </si>
-  <si>
-    <t>Neat but I think it gave me eye strain.</t>
-  </si>
-  <si>
-    <t>Can I just use the barf emoji?</t>
-  </si>
-  <si>
-    <t>I wanted to love it, but I felt so dizzy I hated it.</t>
-  </si>
-  <si>
-    <t>Not bad but I wouldn't buy one.</t>
-  </si>
-  <si>
-    <t>Incredible immersion. It only made me a tiny bit dizzy.</t>
+    <t>Intention to buy Headest</t>
   </si>
 </sst>
 </file>
@@ -264,7 +147,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -573,10 +460,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G101"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="18.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,11 +488,8 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -610,10 +497,10 @@
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>17.399999999999999</v>
@@ -624,11 +511,8 @@
       <c r="G2">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -636,10 +520,10 @@
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>6.25</v>
@@ -651,7 +535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -659,10 +543,10 @@
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>9.26</v>
@@ -673,11 +557,8 @@
       <c r="G4">
         <v>7</v>
       </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -685,10 +566,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>16.78</v>
@@ -700,7 +581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -708,10 +589,10 @@
         <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>38.35</v>
@@ -722,11 +603,8 @@
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -734,10 +612,10 @@
         <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>38.74</v>
@@ -748,11 +626,8 @@
       <c r="G7">
         <v>3</v>
       </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -760,10 +635,10 @@
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8">
         <v>29.14</v>
@@ -774,11 +649,8 @@
       <c r="G8">
         <v>3</v>
       </c>
-      <c r="H8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -786,10 +658,10 @@
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9">
         <v>14.36</v>
@@ -800,11 +672,8 @@
       <c r="G9">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -812,10 +681,10 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -827,7 +696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -835,10 +704,10 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11">
         <v>15.7</v>
@@ -850,7 +719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -858,10 +727,10 @@
         <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12">
         <v>42.73</v>
@@ -872,11 +741,8 @@
       <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -884,10 +750,10 @@
         <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13">
         <v>14.24</v>
@@ -899,7 +765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -907,10 +773,10 @@
         <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14">
         <v>11.17</v>
@@ -921,11 +787,8 @@
       <c r="G14">
         <v>6</v>
       </c>
-      <c r="H14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -933,10 +796,10 @@
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15">
         <v>19.079999999999998</v>
@@ -947,11 +810,8 @@
       <c r="G15">
         <v>5</v>
       </c>
-      <c r="H15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -959,10 +819,10 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16">
         <v>49.25</v>
@@ -974,7 +834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -982,10 +842,10 @@
         <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17">
         <v>32.25</v>
@@ -996,11 +856,8 @@
       <c r="G17">
         <v>5</v>
       </c>
-      <c r="H17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1008,10 +865,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>42.08</v>
@@ -1022,11 +879,8 @@
       <c r="G18">
         <v>8</v>
       </c>
-      <c r="H18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1034,10 +888,10 @@
         <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>21.3</v>
@@ -1048,11 +902,8 @@
       <c r="G19">
         <v>5</v>
       </c>
-      <c r="H19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1060,10 +911,10 @@
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>19.559999999999999</v>
@@ -1075,7 +926,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1083,10 +934,10 @@
         <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21">
         <v>30.17</v>
@@ -1097,11 +948,8 @@
       <c r="G21">
         <v>5</v>
       </c>
-      <c r="H21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1109,10 +957,10 @@
         <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22">
         <v>25.57</v>
@@ -1123,11 +971,8 @@
       <c r="G22">
         <v>8</v>
       </c>
-      <c r="H22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1135,10 +980,10 @@
         <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23">
         <v>39.200000000000003</v>
@@ -1150,7 +995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1158,10 +1003,10 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24">
         <v>42.78</v>
@@ -1172,11 +1017,8 @@
       <c r="G24">
         <v>4</v>
       </c>
-      <c r="H24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1184,10 +1026,10 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>32.409999999999997</v>
@@ -1198,11 +1040,8 @@
       <c r="G25">
         <v>7</v>
       </c>
-      <c r="H25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1210,10 +1049,10 @@
         <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26">
         <v>16.72</v>
@@ -1225,7 +1064,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1233,10 +1072,10 @@
         <v>63</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27">
         <v>17.34</v>
@@ -1247,11 +1086,8 @@
       <c r="G27">
         <v>9</v>
       </c>
-      <c r="H27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1259,10 +1095,10 @@
         <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E28">
         <v>25.84</v>
@@ -1274,7 +1110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1282,10 +1118,10 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29">
         <v>19.399999999999999</v>
@@ -1296,11 +1132,8 @@
       <c r="G29">
         <v>6</v>
       </c>
-      <c r="H29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1308,10 +1141,10 @@
         <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30">
         <v>12.65</v>
@@ -1323,7 +1156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1331,10 +1164,10 @@
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31">
         <v>47.56</v>
@@ -1346,7 +1179,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1354,10 +1187,10 @@
         <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E32">
         <v>14.86</v>
@@ -1368,11 +1201,8 @@
       <c r="G32">
         <v>6</v>
       </c>
-      <c r="H32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1380,10 +1210,10 @@
         <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E33">
         <v>45.61</v>
@@ -1395,7 +1225,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1403,10 +1233,10 @@
         <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34">
         <v>17.27</v>
@@ -1418,7 +1248,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1426,10 +1256,10 @@
         <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E35">
         <v>23.44</v>
@@ -1440,11 +1270,8 @@
       <c r="G35">
         <v>9</v>
       </c>
-      <c r="H35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1452,10 +1279,10 @@
         <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E36">
         <v>17.46</v>
@@ -1466,11 +1293,8 @@
       <c r="G36">
         <v>8</v>
       </c>
-      <c r="H36" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1478,10 +1302,10 @@
         <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E37">
         <v>20.36</v>
@@ -1492,11 +1316,8 @@
       <c r="G37">
         <v>6</v>
       </c>
-      <c r="H37" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1504,10 +1325,10 @@
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E38">
         <v>18.100000000000001</v>
@@ -1519,7 +1340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1527,10 +1348,10 @@
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E39">
         <v>16.97</v>
@@ -1541,11 +1362,8 @@
       <c r="G39">
         <v>4</v>
       </c>
-      <c r="H39" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1553,10 +1371,10 @@
         <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E40">
         <v>12.05</v>
@@ -1568,7 +1386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1576,10 +1394,10 @@
         <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E41">
         <v>32.869999999999997</v>
@@ -1591,7 +1409,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1599,10 +1417,10 @@
         <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E42">
         <v>24.26</v>
@@ -1613,11 +1431,8 @@
       <c r="G42">
         <v>5</v>
       </c>
-      <c r="H42" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1625,10 +1440,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E43">
         <v>42.15</v>
@@ -1639,11 +1454,8 @@
       <c r="G43">
         <v>6</v>
       </c>
-      <c r="H43" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1651,10 +1463,10 @@
         <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44">
         <v>37.6</v>
@@ -1666,7 +1478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1674,10 +1486,10 @@
         <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E45">
         <v>17.48</v>
@@ -1689,7 +1501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1697,10 +1509,10 @@
         <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E46">
         <v>23.48</v>
@@ -1711,11 +1523,8 @@
       <c r="G46">
         <v>5</v>
       </c>
-      <c r="H46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1723,10 +1532,10 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E47">
         <v>13.83</v>
@@ -1738,7 +1547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1746,10 +1555,10 @@
         <v>63</v>
       </c>
       <c r="C48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E48">
         <v>28.56</v>
@@ -1761,7 +1570,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1769,10 +1578,10 @@
         <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E49">
         <v>23.5</v>
@@ -1783,11 +1592,8 @@
       <c r="G49">
         <v>7</v>
       </c>
-      <c r="H49" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1795,10 +1601,10 @@
         <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E50">
         <v>23.69</v>
@@ -1810,7 +1616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1818,10 +1624,10 @@
         <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E51">
         <v>27.96</v>
@@ -1833,7 +1639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1841,10 +1647,10 @@
         <v>51</v>
       </c>
       <c r="C52" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E52">
         <v>7.07</v>
@@ -1855,11 +1661,8 @@
       <c r="G52">
         <v>10</v>
       </c>
-      <c r="H52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1867,10 +1670,10 @@
         <v>43</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E53">
         <v>5.43</v>
@@ -1881,11 +1684,8 @@
       <c r="G53">
         <v>9</v>
       </c>
-      <c r="H53" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1893,10 +1693,10 @@
         <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54">
         <v>17.77</v>
@@ -1908,7 +1708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1916,10 +1716,10 @@
         <v>31</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E55">
         <v>18.809999999999999</v>
@@ -1931,7 +1731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1939,10 +1739,10 @@
         <v>58</v>
       </c>
       <c r="C56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E56">
         <v>25.46</v>
@@ -1953,11 +1753,8 @@
       <c r="G56">
         <v>8</v>
       </c>
-      <c r="H56" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1965,10 +1762,10 @@
         <v>21</v>
       </c>
       <c r="C57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E57">
         <v>13.57</v>
@@ -1980,7 +1777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1988,10 +1785,10 @@
         <v>22</v>
       </c>
       <c r="C58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E58">
         <v>32.86</v>
@@ -2002,11 +1799,8 @@
       <c r="G58">
         <v>5</v>
       </c>
-      <c r="H58" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2014,10 +1808,10 @@
         <v>56</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E59">
         <v>26.47</v>
@@ -2029,7 +1823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2037,10 +1831,10 @@
         <v>36</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E60">
         <v>46.49</v>
@@ -2051,11 +1845,8 @@
       <c r="G60">
         <v>4</v>
       </c>
-      <c r="H60" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2063,10 +1854,10 @@
         <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E61">
         <v>20.2</v>
@@ -2078,7 +1869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2086,10 +1877,10 @@
         <v>21</v>
       </c>
       <c r="C62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E62">
         <v>28.7</v>
@@ -2101,7 +1892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2109,10 +1900,10 @@
         <v>47</v>
       </c>
       <c r="C63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E63">
         <v>30.53</v>
@@ -2124,7 +1915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2132,10 +1923,10 @@
         <v>42</v>
       </c>
       <c r="C64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E64">
         <v>13.38</v>
@@ -2146,11 +1937,8 @@
       <c r="G64">
         <v>10</v>
       </c>
-      <c r="H64" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2158,10 +1946,10 @@
         <v>56</v>
       </c>
       <c r="C65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E65">
         <v>13.06</v>
@@ -2173,7 +1961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2181,10 +1969,10 @@
         <v>51</v>
       </c>
       <c r="C66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E66">
         <v>48.48</v>
@@ -2195,11 +1983,8 @@
       <c r="G66">
         <v>4</v>
       </c>
-      <c r="H66" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2207,10 +1992,10 @@
         <v>52</v>
       </c>
       <c r="C67" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E67">
         <v>33.299999999999997</v>
@@ -2222,7 +2007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2230,10 +2015,10 @@
         <v>20</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E68">
         <v>34.14</v>
@@ -2245,7 +2030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2253,10 +2038,10 @@
         <v>38</v>
       </c>
       <c r="C69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E69">
         <v>22.18</v>
@@ -2267,11 +2052,8 @@
       <c r="G69">
         <v>10</v>
       </c>
-      <c r="H69" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2279,10 +2061,10 @@
         <v>21</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E70">
         <v>36.75</v>
@@ -2293,11 +2075,8 @@
       <c r="G70">
         <v>6</v>
       </c>
-      <c r="H70" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2305,10 +2084,10 @@
         <v>63</v>
       </c>
       <c r="C71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E71">
         <v>16.13</v>
@@ -2319,11 +2098,8 @@
       <c r="G71">
         <v>9</v>
       </c>
-      <c r="H71" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2331,10 +2107,10 @@
         <v>45</v>
       </c>
       <c r="C72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E72">
         <v>19.62</v>
@@ -2345,11 +2121,8 @@
       <c r="G72">
         <v>6</v>
       </c>
-      <c r="H72" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2357,10 +2130,10 @@
         <v>51</v>
       </c>
       <c r="C73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E73">
         <v>29.9</v>
@@ -2371,11 +2144,8 @@
       <c r="G73">
         <v>3</v>
       </c>
-      <c r="H73" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2383,10 +2153,10 @@
         <v>25</v>
       </c>
       <c r="C74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E74">
         <v>28.02</v>
@@ -2398,7 +2168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2406,10 +2176,10 @@
         <v>51</v>
       </c>
       <c r="C75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E75">
         <v>17.47</v>
@@ -2421,7 +2191,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2429,10 +2199,10 @@
         <v>23</v>
       </c>
       <c r="C76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E76">
         <v>21.38</v>
@@ -2443,11 +2213,8 @@
       <c r="G76">
         <v>9</v>
       </c>
-      <c r="H76" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2455,10 +2222,10 @@
         <v>30</v>
       </c>
       <c r="C77" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E77">
         <v>12.15</v>
@@ -2469,11 +2236,8 @@
       <c r="G77">
         <v>10</v>
       </c>
-      <c r="H77" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2481,10 +2245,10 @@
         <v>36</v>
       </c>
       <c r="C78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E78">
         <v>5</v>
@@ -2496,7 +2260,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2504,10 +2268,10 @@
         <v>57</v>
       </c>
       <c r="C79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E79">
         <v>44.7</v>
@@ -2519,7 +2283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2527,10 +2291,10 @@
         <v>43</v>
       </c>
       <c r="C80" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E80">
         <v>37.880000000000003</v>
@@ -2541,11 +2305,8 @@
       <c r="G80">
         <v>5</v>
       </c>
-      <c r="H80" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2553,10 +2314,10 @@
         <v>24</v>
       </c>
       <c r="C81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E81">
         <v>35.93</v>
@@ -2568,7 +2329,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2576,10 +2337,10 @@
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E82">
         <v>19.329999999999998</v>
@@ -2591,7 +2352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2599,10 +2360,10 @@
         <v>25</v>
       </c>
       <c r="C83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E83">
         <v>5.58</v>
@@ -2613,11 +2374,8 @@
       <c r="G83">
         <v>9</v>
       </c>
-      <c r="H83" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2625,10 +2383,10 @@
         <v>41</v>
       </c>
       <c r="C84" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E84">
         <v>34.700000000000003</v>
@@ -2640,7 +2398,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2648,10 +2406,10 @@
         <v>30</v>
       </c>
       <c r="C85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E85">
         <v>31.15</v>
@@ -2662,11 +2420,8 @@
       <c r="G85">
         <v>3</v>
       </c>
-      <c r="H85" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2674,10 +2429,10 @@
         <v>35</v>
       </c>
       <c r="C86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E86">
         <v>10.45</v>
@@ -2689,7 +2444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2697,10 +2452,10 @@
         <v>52</v>
       </c>
       <c r="C87" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E87">
         <v>41.26</v>
@@ -2711,11 +2466,8 @@
       <c r="G87">
         <v>8</v>
       </c>
-      <c r="H87" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2723,10 +2475,10 @@
         <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E88">
         <v>10.46</v>
@@ -2738,7 +2490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2746,10 +2498,10 @@
         <v>25</v>
       </c>
       <c r="C89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E89">
         <v>23.37</v>
@@ -2760,11 +2512,8 @@
       <c r="G89">
         <v>10</v>
       </c>
-      <c r="H89" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2772,10 +2521,10 @@
         <v>35</v>
       </c>
       <c r="C90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E90">
         <v>15.38</v>
@@ -2786,11 +2535,8 @@
       <c r="G90">
         <v>9</v>
       </c>
-      <c r="H90" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2798,10 +2544,10 @@
         <v>48</v>
       </c>
       <c r="C91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D91" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E91">
         <v>20.77</v>
@@ -2813,7 +2559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2821,10 +2567,10 @@
         <v>22</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E92">
         <v>35.409999999999997</v>
@@ -2835,11 +2581,8 @@
       <c r="G92">
         <v>1</v>
       </c>
-      <c r="H92" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2847,10 +2590,10 @@
         <v>39</v>
       </c>
       <c r="C93" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E93">
         <v>17.559999999999999</v>
@@ -2862,7 +2605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2870,10 +2613,10 @@
         <v>55</v>
       </c>
       <c r="C94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E94">
         <v>14.79</v>
@@ -2884,11 +2627,8 @@
       <c r="G94">
         <v>8</v>
       </c>
-      <c r="H94" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2896,10 +2636,10 @@
         <v>38</v>
       </c>
       <c r="C95" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E95">
         <v>40.79</v>
@@ -2911,7 +2651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2919,10 +2659,10 @@
         <v>45</v>
       </c>
       <c r="C96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E96">
         <v>15.91</v>
@@ -2934,7 +2674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2942,10 +2682,10 @@
         <v>22</v>
       </c>
       <c r="C97" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D97" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E97">
         <v>27.53</v>
@@ -2956,11 +2696,8 @@
       <c r="G97">
         <v>6</v>
       </c>
-      <c r="H97" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2968,10 +2705,10 @@
         <v>38</v>
       </c>
       <c r="C98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E98">
         <v>26.54</v>
@@ -2983,7 +2720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -2991,10 +2728,10 @@
         <v>39</v>
       </c>
       <c r="C99" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E99">
         <v>26.02</v>
@@ -3005,11 +2742,8 @@
       <c r="G99">
         <v>7</v>
       </c>
-      <c r="H99" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3017,10 +2751,10 @@
         <v>51</v>
       </c>
       <c r="C100" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E100">
         <v>32.130000000000003</v>
@@ -3032,7 +2766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3040,10 +2774,10 @@
         <v>26</v>
       </c>
       <c r="C101" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E101">
         <v>33.19</v>
@@ -3054,7 +2788,564 @@
       <c r="G101">
         <v>5</v>
       </c>
-      <c r="H101" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36BB92A7-E988-47B2-8216-272C27D07856}">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>14.33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>11.86</v>
+      </c>
+      <c r="B3" s="2">
+        <v>13.78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>12.65</v>
+      </c>
+      <c r="B4" s="2">
+        <v>15.38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>13.52</v>
+      </c>
+      <c r="B5" s="2">
+        <v>13.91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>11.77</v>
+      </c>
+      <c r="B6" s="2">
+        <v>13.31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>11.77</v>
+      </c>
+      <c r="B7" s="2">
+        <v>16.760000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>13.58</v>
+      </c>
+      <c r="B8" s="2">
+        <v>14.73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>12.77</v>
+      </c>
+      <c r="B9" s="2">
+        <v>15.08</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>11.53</v>
+      </c>
+      <c r="B10" s="2">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>12.54</v>
+      </c>
+      <c r="B11" s="2">
+        <v>14.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>11.54</v>
+      </c>
+      <c r="B12" s="2">
+        <v>15.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>11.53</v>
+      </c>
+      <c r="B13" s="2">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>12.24</v>
+      </c>
+      <c r="B14" s="2">
+        <v>15.45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>10.09</v>
+      </c>
+      <c r="B15" s="2">
+        <v>14.28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>10.28</v>
+      </c>
+      <c r="B16" s="2">
+        <v>14.65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD5B06F-FF2B-461B-BF84-0082C969F10E}">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="3" width="37.36328125" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>4</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>5</v>
+      </c>
+      <c r="C24" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>4</v>
+      </c>
+      <c r="C28" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>3</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C2AADCF-5906-4F20-8051-83E6F70CF85A}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
         <v>30</v>
       </c>
     </row>
